--- a/dezhurstva/files/2026-11.xlsx
+++ b/dezhurstva/files/2026-11.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="d"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,11 +75,6 @@
       <color rgb="FF213C56"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="FF637386"/>
-      <sz val="9"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -228,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -282,9 +277,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -663,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF16"/>
+  <dimension ref="A1:AF13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -812,125 +804,125 @@
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="6" t="n"/>
-      <c r="B4" s="7">
+      <c r="B4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(B3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="C4" s="8">
+        <v>Вс</v>
+      </c>
+      <c r="C4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(C3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="D4" s="8">
+        <v>Пн</v>
+      </c>
+      <c r="D4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(D3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="E4" s="7">
+        <v>Вт</v>
+      </c>
+      <c r="E4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(E3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="F4" s="8">
+        <v>Ср</v>
+      </c>
+      <c r="F4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(F3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="G4" s="8">
+        <v>Чт</v>
+      </c>
+      <c r="G4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(G3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="H4" s="7">
+        <v>Пт</v>
+      </c>
+      <c r="H4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(H3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="I4" s="7">
+        <v>Сб</v>
+      </c>
+      <c r="I4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(I3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="J4" s="8">
+        <v>Вс</v>
+      </c>
+      <c r="J4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(J3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="K4" s="8">
+        <v>Пн</v>
+      </c>
+      <c r="K4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(K3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="L4" s="8">
+        <v>Вт</v>
+      </c>
+      <c r="L4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(L3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="M4" s="8">
+        <v>Ср</v>
+      </c>
+      <c r="M4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(M3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="N4" s="8">
+        <v>Чт</v>
+      </c>
+      <c r="N4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(N3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="O4" s="7">
+        <v>Пт</v>
+      </c>
+      <c r="O4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(O3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="P4" s="7">
+        <v>Сб</v>
+      </c>
+      <c r="P4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(P3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="Q4" s="8">
+        <v>Вс</v>
+      </c>
+      <c r="Q4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(Q3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="R4" s="8">
+        <v>Пн</v>
+      </c>
+      <c r="R4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(R3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="S4" s="8">
+        <v>Вт</v>
+      </c>
+      <c r="S4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(S3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="T4" s="8">
+        <v>Ср</v>
+      </c>
+      <c r="T4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(T3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="U4" s="8">
+        <v>Чт</v>
+      </c>
+      <c r="U4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(U3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="V4" s="7">
+        <v>Пт</v>
+      </c>
+      <c r="V4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(V3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="W4" s="7">
+        <v>Сб</v>
+      </c>
+      <c r="W4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(W3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="X4" s="8">
+        <v>Вс</v>
+      </c>
+      <c r="X4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(X3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="Y4" s="8">
+        <v>Пн</v>
+      </c>
+      <c r="Y4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(Y3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="Z4" s="8">
+        <v>Вт</v>
+      </c>
+      <c r="Z4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(Z3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="AA4" s="8">
+        <v>Ср</v>
+      </c>
+      <c r="AA4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(AA3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="AB4" s="8">
+        <v>Чт</v>
+      </c>
+      <c r="AB4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(AB3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="AC4" s="7">
+        <v>Пт</v>
+      </c>
+      <c r="AC4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(AC3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="AD4" s="7">
+        <v>Сб</v>
+      </c>
+      <c r="AD4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(AD3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
-      </c>
-      <c r="AE4" s="8">
+        <v>Вс</v>
+      </c>
+      <c r="AE4" s="8" t="str">
         <f>CHOOSE(WEEKDAY(AE3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
-        <v/>
+        <v>Пн</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -999,7 +991,7 @@
       <c r="AE5" s="11" t="n"/>
       <c r="AF5" s="12">
         <f>COUNTIF(B5:AE5,"+")</f>
-        <v/>
+        <v>7</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -1064,7 +1056,7 @@
       </c>
       <c r="AF6" s="12">
         <f>COUNTIF(B6:AE6,"+")</f>
-        <v/>
+        <v>6</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -1121,7 +1113,7 @@
       <c r="AE7" s="11" t="n"/>
       <c r="AF7" s="12">
         <f>COUNTIF(B7:AE7,"+")</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -1166,7 +1158,7 @@
       <c r="AE8" s="14" t="n"/>
       <c r="AF8" s="12">
         <f>COUNTIF(B8:AE8,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -1223,7 +1215,7 @@
       <c r="AE9" s="11" t="n"/>
       <c r="AF9" s="12">
         <f>COUNTIF(B9:AE9,"+")</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -1280,7 +1272,7 @@
       <c r="AE10" s="14" t="n"/>
       <c r="AF10" s="12">
         <f>COUNTIF(B10:AE10,"+")</f>
-        <v/>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -1321,7 +1313,7 @@
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="12">
         <f>COUNTIF(B11:AE11,"+")</f>
-        <v/>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
@@ -1382,7 +1374,7 @@
       <c r="AE12" s="14" t="n"/>
       <c r="AF12" s="12">
         <f>COUNTIF(B12:AE12,"+")</f>
-        <v/>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="23" customHeight="1">
@@ -1393,152 +1385,136 @@
       </c>
       <c r="B13" s="18">
         <f>COUNTIF(B5:B12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C13" s="18">
         <f>COUNTIF(C5:C12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D13" s="18">
         <f>COUNTIF(D5:D12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="E13" s="18">
         <f>COUNTIF(E5:E12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F13" s="18">
         <f>COUNTIF(F5:F12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="G13" s="18">
         <f>COUNTIF(G5:G12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H13" s="18">
         <f>COUNTIF(H5:H12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I13" s="18">
         <f>COUNTIF(I5:I12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="J13" s="18">
         <f>COUNTIF(J5:J12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="K13" s="18">
         <f>COUNTIF(K5:K12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="L13" s="18">
         <f>COUNTIF(L5:L12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="M13" s="18">
         <f>COUNTIF(M5:M12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="N13" s="18">
         <f>COUNTIF(N5:N12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="O13" s="18">
         <f>COUNTIF(O5:O12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="P13" s="18">
         <f>COUNTIF(P5:P12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Q13" s="18">
         <f>COUNTIF(Q5:Q12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="R13" s="18">
         <f>COUNTIF(R5:R12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="S13" s="18">
         <f>COUNTIF(S5:S12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T13" s="18">
         <f>COUNTIF(T5:T12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="U13" s="18">
         <f>COUNTIF(U5:U12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="V13" s="18">
         <f>COUNTIF(V5:V12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="W13" s="18">
         <f>COUNTIF(W5:W12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="X13" s="18">
         <f>COUNTIF(X5:X12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y13" s="18">
         <f>COUNTIF(Y5:Y12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="Z13" s="18">
         <f>COUNTIF(Z5:Z12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AA13" s="18">
         <f>COUNTIF(AA5:AA12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AB13" s="18">
         <f>COUNTIF(AB5:AB12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AC13" s="18">
         <f>COUNTIF(AC5:AC12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AD13" s="18">
         <f>COUNTIF(AD5:AD12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AE13" s="18">
         <f>COUNTIF(AE5:AE12,"+")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="AF13" s="19">
         <f>SUM(B13:AE13)</f>
-        <v/>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="7" customHeight="1"/>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="20" t="inlineStr">
-        <is>
-          <t>+ — дежурство; серым выделены субботы, воскресенья, праздники 4 ноября (производственный календарь РФ); отпуск — Лекерова 04–16.11.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
-        <is>
-          <t>Будни: 16:18–08:00 (15 ч 42 мин). Выходные и праздники: 08:00–08:00 (24 ч).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="4">
     <mergeCell ref="A1:AF1"/>
+    <mergeCell ref="E7:Q7"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="E7:Q7"/>
-    <mergeCell ref="A15:AF15"/>
-    <mergeCell ref="A16:AF16"/>
   </mergeCells>
   <conditionalFormatting sqref="B13:AE13">
     <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="0">

--- a/dezhurstva/files/2026-11.xlsx
+++ b/dezhurstva/files/2026-11.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AF13"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1278,7 +1278,7 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>ДАВЫДОВА</t>
+          <t>ОМУТОВ</t>
         </is>
       </c>
       <c r="B11" s="10" t="n"/>
@@ -1288,9 +1288,17 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="11" t="n"/>
       <c r="H11" s="10" t="n"/>
-      <c r="I11" s="10" t="n"/>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
       <c r="J11" s="11" t="n"/>
-      <c r="K11" s="11" t="n"/>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="n"/>
       <c r="M11" s="11" t="n"/>
       <c r="N11" s="11" t="n"/>
@@ -1298,217 +1306,168 @@
       <c r="P11" s="10" t="n"/>
       <c r="Q11" s="11" t="n"/>
       <c r="R11" s="11" t="n"/>
-      <c r="S11" s="11" t="n"/>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
       <c r="T11" s="11" t="n"/>
       <c r="U11" s="11" t="n"/>
       <c r="V11" s="10" t="n"/>
       <c r="W11" s="10" t="n"/>
-      <c r="X11" s="11" t="n"/>
+      <c r="X11" s="11" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
       <c r="Y11" s="11" t="n"/>
       <c r="Z11" s="11" t="n"/>
       <c r="AA11" s="11" t="n"/>
       <c r="AB11" s="11" t="n"/>
-      <c r="AC11" s="10" t="n"/>
+      <c r="AC11" s="10" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
       <c r="AD11" s="10" t="n"/>
       <c r="AE11" s="11" t="n"/>
       <c r="AF11" s="12">
         <f>COUNTIF(B11:AE11,"+")</f>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>ОМУТОВ</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="10" t="n"/>
-      <c r="F12" s="14" t="n"/>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="14" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
-      <c r="N12" s="14" t="n"/>
-      <c r="O12" s="10" t="n"/>
-      <c r="P12" s="10" t="n"/>
-      <c r="Q12" s="14" t="n"/>
-      <c r="R12" s="14" t="n"/>
-      <c r="S12" s="14" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="T12" s="14" t="n"/>
-      <c r="U12" s="14" t="n"/>
-      <c r="V12" s="10" t="n"/>
-      <c r="W12" s="10" t="n"/>
-      <c r="X12" s="14" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="Y12" s="14" t="n"/>
-      <c r="Z12" s="14" t="n"/>
-      <c r="AA12" s="14" t="n"/>
-      <c r="AB12" s="14" t="n"/>
-      <c r="AC12" s="10" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="AD12" s="10" t="n"/>
-      <c r="AE12" s="14" t="n"/>
-      <c r="AF12" s="12">
-        <f>COUNTIF(B12:AE12,"+")</f>
-        <v>5</v>
+    <row r="12" ht="23" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>Дежурных за день</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>COUNTIF(B5:B11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="18">
+        <f>COUNTIF(C5:C11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="D12" s="18">
+        <f>COUNTIF(D5:D11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="E12" s="18">
+        <f>COUNTIF(E5:E11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="F12" s="18">
+        <f>COUNTIF(F5:F11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="G12" s="18">
+        <f>COUNTIF(G5:G11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="18">
+        <f>COUNTIF(H5:H11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="I12" s="18">
+        <f>COUNTIF(I5:I11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="J12" s="18">
+        <f>COUNTIF(J5:J11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="K12" s="18">
+        <f>COUNTIF(K5:K11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="L12" s="18">
+        <f>COUNTIF(L5:L11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="M12" s="18">
+        <f>COUNTIF(M5:M11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="N12" s="18">
+        <f>COUNTIF(N5:N11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="O12" s="18">
+        <f>COUNTIF(O5:O11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="P12" s="18">
+        <f>COUNTIF(P5:P11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="Q12" s="18">
+        <f>COUNTIF(Q5:Q11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="R12" s="18">
+        <f>COUNTIF(R5:R11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="S12" s="18">
+        <f>COUNTIF(S5:S11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="T12" s="18">
+        <f>COUNTIF(T5:T11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="U12" s="18">
+        <f>COUNTIF(U5:U11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="V12" s="18">
+        <f>COUNTIF(V5:V11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="W12" s="18">
+        <f>COUNTIF(W5:W11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="X12" s="18">
+        <f>COUNTIF(X5:X11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="Y12" s="18">
+        <f>COUNTIF(Y5:Y11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="Z12" s="18">
+        <f>COUNTIF(Z5:Z11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="AA12" s="18">
+        <f>COUNTIF(AA5:AA11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="AB12" s="18">
+        <f>COUNTIF(AB5:AB11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="AC12" s="18">
+        <f>COUNTIF(AC5:AC11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="AD12" s="18">
+        <f>COUNTIF(AD5:AD11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="AE12" s="18">
+        <f>COUNTIF(AE5:AE11,"+")</f>
+        <v>1</v>
+      </c>
+      <c r="AF12" s="19">
+        <f>SUM(B12:AE12)</f>
+        <v>30</v>
       </c>
     </row>
-    <row r="13" ht="23" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>Дежурных за день</t>
-        </is>
-      </c>
-      <c r="B13" s="18">
-        <f>COUNTIF(B5:B12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="C13" s="18">
-        <f>COUNTIF(C5:C12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="D13" s="18">
-        <f>COUNTIF(D5:D12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="E13" s="18">
-        <f>COUNTIF(E5:E12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="F13" s="18">
-        <f>COUNTIF(F5:F12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="G13" s="18">
-        <f>COUNTIF(G5:G12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="H13" s="18">
-        <f>COUNTIF(H5:H12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="I13" s="18">
-        <f>COUNTIF(I5:I12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="J13" s="18">
-        <f>COUNTIF(J5:J12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="K13" s="18">
-        <f>COUNTIF(K5:K12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="L13" s="18">
-        <f>COUNTIF(L5:L12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="M13" s="18">
-        <f>COUNTIF(M5:M12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="N13" s="18">
-        <f>COUNTIF(N5:N12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="O13" s="18">
-        <f>COUNTIF(O5:O12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="P13" s="18">
-        <f>COUNTIF(P5:P12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="18">
-        <f>COUNTIF(Q5:Q12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="R13" s="18">
-        <f>COUNTIF(R5:R12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="S13" s="18">
-        <f>COUNTIF(S5:S12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="T13" s="18">
-        <f>COUNTIF(T5:T12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="U13" s="18">
-        <f>COUNTIF(U5:U12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="V13" s="18">
-        <f>COUNTIF(V5:V12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="W13" s="18">
-        <f>COUNTIF(W5:W12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="X13" s="18">
-        <f>COUNTIF(X5:X12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="Y13" s="18">
-        <f>COUNTIF(Y5:Y12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="Z13" s="18">
-        <f>COUNTIF(Z5:Z12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="AA13" s="18">
-        <f>COUNTIF(AA5:AA12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="AB13" s="18">
-        <f>COUNTIF(AB5:AB12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="AC13" s="18">
-        <f>COUNTIF(AC5:AC12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="AD13" s="18">
-        <f>COUNTIF(AD5:AD12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="AE13" s="18">
-        <f>COUNTIF(AE5:AE12,"+")</f>
-        <v>1</v>
-      </c>
-      <c r="AF13" s="19">
-        <f>SUM(B13:AE13)</f>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" ht="7" customHeight="1"/>
+    <row r="13" ht="7" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:AF1"/>
@@ -1516,7 +1475,7 @@
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="AF3:AF4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B13:AE13">
+  <conditionalFormatting sqref="B12:AE12">
     <cfRule type="cellIs" priority="1" operator="notEqual" dxfId="0">
       <formula>1</formula>
     </cfRule>

--- a/dezhurstva/files/2026-11.xlsx
+++ b/dezhurstva/files/2026-11.xlsx
@@ -114,7 +114,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -123,107 +123,49 @@
       <diagonal/>
     </border>
     <border>
-      <right style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
-    </border>
-    <border>
+      <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
+      <right style="thin"/>
+      <top style="thin"/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FFFFFFFF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFFFFFF"/>
-      </bottom>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -231,51 +173,46 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -796,134 +733,135 @@
       <c r="AE3" s="4" t="n">
         <v>46356</v>
       </c>
-      <c r="AF3" s="5" t="inlineStr">
+      <c r="AF3" s="2" t="inlineStr">
         <is>
           <t>Всего</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="7" t="str">
+      <c r="A4" s="5" t="n"/>
+      <c r="B4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(B3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Вс</v>
       </c>
-      <c r="C4" s="8" t="str">
+      <c r="C4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(C3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Пн</v>
       </c>
-      <c r="D4" s="8" t="str">
+      <c r="D4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(D3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Вт</v>
       </c>
-      <c r="E4" s="7" t="str">
+      <c r="E4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(E3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Ср</v>
       </c>
-      <c r="F4" s="8" t="str">
+      <c r="F4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(F3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Чт</v>
       </c>
-      <c r="G4" s="8" t="str">
+      <c r="G4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(G3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Пт</v>
       </c>
-      <c r="H4" s="7" t="str">
+      <c r="H4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(H3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Сб</v>
       </c>
-      <c r="I4" s="7" t="str">
+      <c r="I4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(I3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Вс</v>
       </c>
-      <c r="J4" s="8" t="str">
+      <c r="J4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(J3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Пн</v>
       </c>
-      <c r="K4" s="8" t="str">
+      <c r="K4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(K3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Вт</v>
       </c>
-      <c r="L4" s="8" t="str">
+      <c r="L4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(L3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Ср</v>
       </c>
-      <c r="M4" s="8" t="str">
+      <c r="M4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(M3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Чт</v>
       </c>
-      <c r="N4" s="8" t="str">
+      <c r="N4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(N3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Пт</v>
       </c>
-      <c r="O4" s="7" t="str">
+      <c r="O4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(O3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Сб</v>
       </c>
-      <c r="P4" s="7" t="str">
+      <c r="P4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(P3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Вс</v>
       </c>
-      <c r="Q4" s="8" t="str">
+      <c r="Q4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(Q3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Пн</v>
       </c>
-      <c r="R4" s="8" t="str">
+      <c r="R4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(R3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Вт</v>
       </c>
-      <c r="S4" s="8" t="str">
+      <c r="S4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(S3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Ср</v>
       </c>
-      <c r="T4" s="8" t="str">
+      <c r="T4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(T3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Чт</v>
       </c>
-      <c r="U4" s="8" t="str">
+      <c r="U4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(U3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Пт</v>
       </c>
-      <c r="V4" s="7" t="str">
+      <c r="V4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(V3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Сб</v>
       </c>
-      <c r="W4" s="7" t="str">
+      <c r="W4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(W3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Вс</v>
       </c>
-      <c r="X4" s="8" t="str">
+      <c r="X4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(X3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Пн</v>
       </c>
-      <c r="Y4" s="8" t="str">
+      <c r="Y4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(Y3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Вт</v>
       </c>
-      <c r="Z4" s="8" t="str">
+      <c r="Z4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(Z3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Ср</v>
       </c>
-      <c r="AA4" s="8" t="str">
+      <c r="AA4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(AA3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Чт</v>
       </c>
-      <c r="AB4" s="8" t="str">
+      <c r="AB4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(AB3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Пт</v>
       </c>
-      <c r="AC4" s="7" t="str">
+      <c r="AC4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(AC3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Сб</v>
       </c>
-      <c r="AD4" s="7" t="str">
+      <c r="AD4" s="6" t="str">
         <f>CHOOSE(WEEKDAY(AD3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Вс</v>
       </c>
-      <c r="AE4" s="8" t="str">
+      <c r="AE4" s="7" t="str">
         <f>CHOOSE(WEEKDAY(AE3,2),"Пн","Вт","Ср","Чт","Пт","Сб","Вс")</f>
         <v>Пн</v>
       </c>
+      <c r="AF4" s="8" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -1462,7 +1400,7 @@
         <f>COUNTIF(AE5:AE11,"+")</f>
         <v>1</v>
       </c>
-      <c r="AF12" s="19">
+      <c r="AF12" s="18">
         <f>SUM(B12:AE12)</f>
         <v>30</v>
       </c>

--- a/dezhurstva/files/2026-11.xlsx
+++ b/dezhurstva/files/2026-11.xlsx
@@ -44,24 +44,24 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF213C56"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF213C56"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <color rgb="FF203449"/>
-      <sz val="10.5"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="FF126E69"/>
-      <sz val="17"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="FF213C56"/>
-      <sz val="12"/>
+      <sz val="22"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -90,7 +90,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCFD9E2"/>
+        <fgColor rgb="FFBCC8D4"/>
       </patternFill>
     </fill>
     <fill>
@@ -110,7 +110,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAD4A3"/>
+        <fgColor rgb="FFDFC385"/>
       </patternFill>
     </fill>
   </fills>
@@ -173,36 +173,36 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -595,37 +595,37 @@
   <dimension ref="A1:AF12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="3.7" customWidth="1" min="2" max="2"/>
-    <col width="3.7" customWidth="1" min="3" max="3"/>
-    <col width="3.7" customWidth="1" min="4" max="4"/>
-    <col width="3.7" customWidth="1" min="5" max="5"/>
-    <col width="3.7" customWidth="1" min="6" max="6"/>
-    <col width="3.7" customWidth="1" min="7" max="7"/>
-    <col width="3.7" customWidth="1" min="8" max="8"/>
-    <col width="3.7" customWidth="1" min="9" max="9"/>
-    <col width="3.7" customWidth="1" min="10" max="10"/>
-    <col width="3.7" customWidth="1" min="11" max="11"/>
-    <col width="3.7" customWidth="1" min="12" max="12"/>
-    <col width="3.7" customWidth="1" min="13" max="13"/>
-    <col width="3.7" customWidth="1" min="14" max="14"/>
-    <col width="3.7" customWidth="1" min="15" max="15"/>
-    <col width="3.7" customWidth="1" min="16" max="16"/>
-    <col width="3.7" customWidth="1" min="17" max="17"/>
-    <col width="3.7" customWidth="1" min="18" max="18"/>
-    <col width="3.7" customWidth="1" min="19" max="19"/>
-    <col width="3.7" customWidth="1" min="20" max="20"/>
-    <col width="3.7" customWidth="1" min="21" max="21"/>
-    <col width="3.7" customWidth="1" min="22" max="22"/>
-    <col width="3.7" customWidth="1" min="23" max="23"/>
-    <col width="3.7" customWidth="1" min="24" max="24"/>
-    <col width="3.7" customWidth="1" min="25" max="25"/>
-    <col width="3.7" customWidth="1" min="26" max="26"/>
-    <col width="3.7" customWidth="1" min="27" max="27"/>
-    <col width="3.7" customWidth="1" min="28" max="28"/>
-    <col width="3.7" customWidth="1" min="29" max="29"/>
-    <col width="3.7" customWidth="1" min="30" max="30"/>
-    <col width="3.7" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+    <col width="3.6" customWidth="1" min="25" max="25"/>
+    <col width="3.6" customWidth="1" min="26" max="26"/>
+    <col width="3.6" customWidth="1" min="27" max="27"/>
+    <col width="3.6" customWidth="1" min="28" max="28"/>
+    <col width="3.6" customWidth="1" min="29" max="29"/>
+    <col width="3.6" customWidth="1" min="30" max="30"/>
+    <col width="3.6" customWidth="1" min="31" max="31"/>
     <col width="6.4" customWidth="1" min="32" max="32"/>
   </cols>
   <sheetData>
@@ -637,7 +637,7 @@
       </c>
     </row>
     <row r="2" ht="7" customHeight="1"/>
-    <row r="3" ht="19" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Врач</t>
@@ -863,7 +863,7 @@
       </c>
       <c r="AF4" s="8" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>КЛЕПИКОВ</t>
@@ -932,7 +932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="36" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>КАРДАШИНА</t>
@@ -997,7 +997,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="36" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>ЛЕКЕРОВА</t>
@@ -1054,7 +1054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="36" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>ХАМАТНУРОВА</t>
@@ -1099,7 +1099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>ЛЕОНАРД</t>
@@ -1156,7 +1156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
           <t>АЛЕКЕШОВА</t>
@@ -1213,7 +1213,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>ОМУТОВ</t>
@@ -1418,7 +1418,8 @@
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.315" right="0.315" top="0.315" bottom="0.315" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>